--- a/tool/track-aggregator/template/テスト結果.xlsx
+++ b/tool/track-aggregator/template/テスト結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\businessImprovement\tool\結果集計\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06317B3E-1A39-4834-9906-4727E30BE136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA9FA05-2441-492A-BE2F-9E2BE57877BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{4ED45D7B-593F-44CB-A79B-DA86FA14B806}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4ED45D7B-593F-44CB-A79B-DA86FA14B806}"/>
   </bookViews>
   <sheets>
     <sheet name="サマリ-ユーザー別" sheetId="23" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
   <si>
     <t>会社名</t>
     <rPh sb="0" eb="3">
@@ -168,16 +168,6 @@
   <si>
     <t>◆ユーザ別</t>
     <rPh sb="4" eb="5">
-      <t>ベツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆科目別</t>
-    <rPh sb="1" eb="3">
-      <t>カモク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
       <t>ベツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1019,7 +1009,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1052,10 +1042,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -1098,7 +1088,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
@@ -1136,7 +1126,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
@@ -1174,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">

--- a/tool/track-aggregator/template/テスト結果.xlsx
+++ b/tool/track-aggregator/template/テスト結果.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA9FA05-2441-492A-BE2F-9E2BE57877BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F982E81-F522-46E8-BAE9-EE8DED6C0B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4ED45D7B-593F-44CB-A79B-DA86FA14B806}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'サマリ-ユーザー別'!$A$3:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'詳細-クラス別'!$B$3:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'詳細-ユーザ別'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'詳細-ユーザ別'!$A$3:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'詳細-ランク別'!$B$3:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'詳細-会社別'!$B$3:$B$3</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="23">
   <si>
     <t>会社名</t>
     <rPh sb="0" eb="3">
@@ -174,10 +174,6 @@
   </si>
   <si>
     <t>{問題データ}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -997,17 +993,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF22EA9-5580-4F5A-AF94-ADDD1EAFF751}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.296875" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.69921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.69921875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="15.69921875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.69921875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.69921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.69921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
@@ -1015,17 +1011,15 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1041,14 +1035,11 @@
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1056,8 +1047,7 @@
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
